--- a/public/report/MonthReport.xlsx
+++ b/public/report/MonthReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Test\19-5Restful+API\RestfulAPI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\test\SEEMS_EMS\public\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB3B713-B502-4C44-9BA1-4132726BBEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58CF1F9-82D4-47D6-98D0-EA260C54C97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="735" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月報" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>日
 (Day)</t>
@@ -133,13 +133,6 @@
   </si>
   <si>
     <t>Minute</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>###</t>
-  </si>
-  <si>
-    <t>###</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -278,10 +271,6 @@
 (kWh)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
-  <si>
-    <t>p</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
@@ -1145,29 +1134,32 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1204,9 +1196,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1508,25 +1497,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>744</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1796,99 +1785,6 @@
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="31"/>
-                <c:pt idx="0">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>91</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2224,99 +2120,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
-                <c:pt idx="0">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>95.5</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2360,99 +2163,6 @@
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="31"/>
-                <c:pt idx="0">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>99</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2496,99 +2206,6 @@
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="31"/>
-                <c:pt idx="0">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>100</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4823,7 +4440,7 @@
     <row r="2" spans="3:29" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="3:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="61" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" s="62"/>
       <c r="E3" s="62"/>
@@ -4841,82 +4458,82 @@
       <c r="Q3" s="62"/>
       <c r="R3" s="62"/>
       <c r="S3" s="63"/>
-      <c r="T3" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="W3" s="73"/>
-      <c r="X3" s="73"/>
-      <c r="Y3" s="73"/>
-      <c r="Z3" s="73"/>
-      <c r="AA3" s="73"/>
-      <c r="AB3" s="73"/>
-      <c r="AC3" s="74"/>
+      <c r="T3" s="73" t="s">
+        <v>16</v>
+      </c>
+      <c r="U3" s="74"/>
+      <c r="V3" s="74"/>
+      <c r="W3" s="74"/>
+      <c r="X3" s="74"/>
+      <c r="Y3" s="74"/>
+      <c r="Z3" s="74"/>
+      <c r="AA3" s="74"/>
+      <c r="AB3" s="74"/>
+      <c r="AC3" s="75"/>
     </row>
     <row r="4" spans="3:29" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="64" t="s">
+      <c r="C4" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="66" t="s">
+      <c r="D4" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="64" t="s">
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="69"/>
-      <c r="M4" s="64" t="s">
+      <c r="L4" s="71"/>
+      <c r="M4" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="69"/>
-      <c r="O4" s="84"/>
-      <c r="P4" s="64" t="s">
+      <c r="N4" s="71"/>
+      <c r="O4" s="72"/>
+      <c r="P4" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="70" t="s">
+      <c r="Q4" s="71"/>
+      <c r="R4" s="71"/>
+      <c r="S4" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="T4" s="75" t="s">
-        <v>30</v>
-      </c>
-      <c r="U4" s="77" t="s">
+      <c r="T4" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="U4" s="78" t="s">
+        <v>19</v>
+      </c>
+      <c r="V4" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="W4" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="V4" s="79" t="s">
+      <c r="X4" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="W4" s="79" t="s">
+      <c r="Y4" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="X4" s="81" t="s">
+      <c r="Z4" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="Y4" s="79" t="s">
+      <c r="AA4" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Z4" s="81" t="s">
+      <c r="AB4" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="AA4" s="79" t="s">
+      <c r="AC4" s="83" t="s">
         <v>27</v>
-      </c>
-      <c r="AB4" s="81" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC4" s="82" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="3:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="65"/>
+      <c r="C5" s="68"/>
       <c r="D5" s="7">
         <v>1</v>
       </c>
@@ -4962,1815 +4579,704 @@
       <c r="R5" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="S5" s="71"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="80"/>
-      <c r="W5" s="80"/>
-      <c r="X5" s="80"/>
-      <c r="Y5" s="80"/>
-      <c r="Z5" s="80"/>
-      <c r="AA5" s="80"/>
-      <c r="AB5" s="80"/>
-      <c r="AC5" s="83"/>
+      <c r="S5" s="70"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="81"/>
+      <c r="W5" s="81"/>
+      <c r="X5" s="81"/>
+      <c r="Y5" s="81"/>
+      <c r="Z5" s="81"/>
+      <c r="AA5" s="81"/>
+      <c r="AB5" s="81"/>
+      <c r="AC5" s="84"/>
     </row>
     <row r="6" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C6" s="17">
         <v>1</v>
       </c>
-      <c r="D6" s="18">
-        <v>24</v>
-      </c>
-      <c r="E6" s="19">
-        <v>24</v>
-      </c>
-      <c r="F6" s="19">
-        <v>5</v>
-      </c>
-      <c r="G6" s="19">
-        <v>5</v>
-      </c>
-      <c r="H6" s="19">
-        <v>5</v>
-      </c>
-      <c r="I6" s="19">
-        <v>5</v>
-      </c>
-      <c r="J6" s="13">
-        <v>5</v>
-      </c>
-      <c r="K6" s="35">
-        <v>0</v>
-      </c>
-      <c r="L6" s="38">
-        <v>0</v>
-      </c>
-      <c r="M6" s="20">
-        <v>100</v>
-      </c>
-      <c r="N6" s="21">
-        <v>99</v>
-      </c>
-      <c r="O6" s="13">
-        <v>95.5</v>
-      </c>
-      <c r="P6" s="25">
-        <v>34.567</v>
-      </c>
-      <c r="Q6" s="26">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R6" s="41">
-        <f>P6-Q6</f>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S6" s="44">
-        <f>Q6/P6*100</f>
-        <v>91</v>
-      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="44"/>
       <c r="T6" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="U6" s="3">
-        <v>3600</v>
-      </c>
-      <c r="V6" s="3">
-        <v>100</v>
-      </c>
-      <c r="W6" s="3">
-        <v>500</v>
-      </c>
-      <c r="X6" s="3">
-        <v>500</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>500</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>500</v>
-      </c>
-      <c r="AA6" s="3">
-        <v>500</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>500</v>
-      </c>
-      <c r="AC6" s="5">
-        <v>500</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="5"/>
     </row>
     <row r="7" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C7" s="16">
         <v>2</v>
       </c>
-      <c r="D7" s="6">
-        <v>24</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="36">
-        <v>0</v>
-      </c>
-      <c r="L7" s="39">
-        <v>0</v>
-      </c>
-      <c r="M7" s="15">
-        <v>100</v>
-      </c>
-      <c r="N7" s="14">
-        <v>99</v>
-      </c>
-      <c r="O7" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P7" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R7" s="42">
-        <f t="shared" ref="R7:R36" si="0">P7-Q7</f>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S7" s="45">
-        <f t="shared" ref="S7:S37" si="1">Q7/P7*100</f>
-        <v>91</v>
-      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="45"/>
       <c r="T7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC7" s="5" t="s">
-        <v>16</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="5"/>
     </row>
     <row r="8" spans="3:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C8" s="16">
         <v>3</v>
       </c>
-      <c r="D8" s="6">
-        <v>24</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0</v>
-      </c>
-      <c r="K8" s="36">
-        <v>0</v>
-      </c>
-      <c r="L8" s="39">
-        <v>0</v>
-      </c>
-      <c r="M8" s="15">
-        <v>100</v>
-      </c>
-      <c r="N8" s="14">
-        <v>99</v>
-      </c>
-      <c r="O8" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P8" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R8" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S8" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="42"/>
+      <c r="S8" s="45"/>
       <c r="T8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="V8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="W8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="X8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC8" s="9" t="s">
-        <v>16</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="8"/>
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="9"/>
     </row>
     <row r="9" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C9" s="16">
         <v>4</v>
       </c>
-      <c r="D9" s="6">
-        <v>24</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0</v>
-      </c>
-      <c r="K9" s="36">
-        <v>0</v>
-      </c>
-      <c r="L9" s="39">
-        <v>0</v>
-      </c>
-      <c r="M9" s="15">
-        <v>100</v>
-      </c>
-      <c r="N9" s="14">
-        <v>99</v>
-      </c>
-      <c r="O9" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P9" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R9" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S9" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="45"/>
     </row>
     <row r="10" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C10" s="16">
         <v>5</v>
       </c>
-      <c r="D10" s="6">
-        <v>24</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5">
-        <v>0</v>
-      </c>
-      <c r="K10" s="36">
-        <v>0</v>
-      </c>
-      <c r="L10" s="39">
-        <v>0</v>
-      </c>
-      <c r="M10" s="15">
-        <v>100</v>
-      </c>
-      <c r="N10" s="14">
-        <v>99</v>
-      </c>
-      <c r="O10" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P10" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R10" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S10" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="42"/>
+      <c r="S10" s="45"/>
     </row>
     <row r="11" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C11" s="16">
         <v>6</v>
       </c>
-      <c r="D11" s="6">
-        <v>24</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5">
-        <v>0</v>
-      </c>
-      <c r="K11" s="36">
-        <v>0</v>
-      </c>
-      <c r="L11" s="39">
-        <v>0</v>
-      </c>
-      <c r="M11" s="15">
-        <v>100</v>
-      </c>
-      <c r="N11" s="14">
-        <v>99</v>
-      </c>
-      <c r="O11" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P11" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R11" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S11" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="45"/>
     </row>
     <row r="12" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C12" s="16">
         <v>7</v>
       </c>
-      <c r="D12" s="6">
-        <v>24</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5">
-        <v>0</v>
-      </c>
-      <c r="K12" s="36">
-        <v>0</v>
-      </c>
-      <c r="L12" s="39">
-        <v>0</v>
-      </c>
-      <c r="M12" s="15">
-        <v>100</v>
-      </c>
-      <c r="N12" s="14">
-        <v>99</v>
-      </c>
-      <c r="O12" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P12" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q12" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R12" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S12" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="42"/>
+      <c r="S12" s="45"/>
     </row>
     <row r="13" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C13" s="16">
         <v>8</v>
       </c>
-      <c r="D13" s="6">
-        <v>24</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5">
-        <v>0</v>
-      </c>
-      <c r="K13" s="36">
-        <v>0</v>
-      </c>
-      <c r="L13" s="39">
-        <v>0</v>
-      </c>
-      <c r="M13" s="15">
-        <v>100</v>
-      </c>
-      <c r="N13" s="14">
-        <v>99</v>
-      </c>
-      <c r="O13" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P13" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q13" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R13" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S13" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="45"/>
     </row>
     <row r="14" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C14" s="16">
         <v>9</v>
       </c>
-      <c r="D14" s="6">
-        <v>24</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5">
-        <v>0</v>
-      </c>
-      <c r="K14" s="36">
-        <v>0</v>
-      </c>
-      <c r="L14" s="39">
-        <v>0</v>
-      </c>
-      <c r="M14" s="15">
-        <v>100</v>
-      </c>
-      <c r="N14" s="14">
-        <v>99</v>
-      </c>
-      <c r="O14" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P14" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R14" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S14" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="45"/>
     </row>
     <row r="15" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C15" s="16">
         <v>10</v>
       </c>
-      <c r="D15" s="6">
-        <v>24</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5">
-        <v>0</v>
-      </c>
-      <c r="K15" s="36">
-        <v>0</v>
-      </c>
-      <c r="L15" s="39">
-        <v>0</v>
-      </c>
-      <c r="M15" s="15">
-        <v>100</v>
-      </c>
-      <c r="N15" s="14">
-        <v>99</v>
-      </c>
-      <c r="O15" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P15" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q15" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R15" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S15" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="45"/>
     </row>
     <row r="16" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C16" s="16">
         <v>11</v>
       </c>
-      <c r="D16" s="6">
-        <v>24</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5">
-        <v>0</v>
-      </c>
-      <c r="K16" s="36">
-        <v>0</v>
-      </c>
-      <c r="L16" s="39">
-        <v>0</v>
-      </c>
-      <c r="M16" s="15">
-        <v>100</v>
-      </c>
-      <c r="N16" s="14">
-        <v>99</v>
-      </c>
-      <c r="O16" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P16" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q16" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R16" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S16" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="45"/>
     </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C17" s="16">
         <v>12</v>
       </c>
-      <c r="D17" s="6">
-        <v>24</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5">
-        <v>0</v>
-      </c>
-      <c r="K17" s="36">
-        <v>0</v>
-      </c>
-      <c r="L17" s="39">
-        <v>0</v>
-      </c>
-      <c r="M17" s="15">
-        <v>100</v>
-      </c>
-      <c r="N17" s="14">
-        <v>99</v>
-      </c>
-      <c r="O17" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P17" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q17" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R17" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S17" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="45"/>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C18" s="16">
         <v>13</v>
       </c>
-      <c r="D18" s="6">
-        <v>24</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-      <c r="J18" s="5">
-        <v>0</v>
-      </c>
-      <c r="K18" s="36">
-        <v>0</v>
-      </c>
-      <c r="L18" s="39">
-        <v>0</v>
-      </c>
-      <c r="M18" s="15">
-        <v>100</v>
-      </c>
-      <c r="N18" s="14">
-        <v>99</v>
-      </c>
-      <c r="O18" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P18" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q18" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R18" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S18" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="45"/>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C19" s="16">
         <v>14</v>
       </c>
-      <c r="D19" s="6">
-        <v>24</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5">
-        <v>0</v>
-      </c>
-      <c r="K19" s="36">
-        <v>0</v>
-      </c>
-      <c r="L19" s="39">
-        <v>0</v>
-      </c>
-      <c r="M19" s="15">
-        <v>100</v>
-      </c>
-      <c r="N19" s="14">
-        <v>99</v>
-      </c>
-      <c r="O19" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P19" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q19" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R19" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S19" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="42"/>
+      <c r="S19" s="45"/>
     </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C20" s="16">
         <v>15</v>
       </c>
-      <c r="D20" s="6">
-        <v>24</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="5">
-        <v>0</v>
-      </c>
-      <c r="K20" s="36">
-        <v>0</v>
-      </c>
-      <c r="L20" s="39">
-        <v>0</v>
-      </c>
-      <c r="M20" s="15">
-        <v>100</v>
-      </c>
-      <c r="N20" s="14">
-        <v>99</v>
-      </c>
-      <c r="O20" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P20" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q20" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R20" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S20" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="45"/>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C21" s="16">
         <v>16</v>
       </c>
-      <c r="D21" s="6">
-        <v>24</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="5">
-        <v>0</v>
-      </c>
-      <c r="K21" s="36">
-        <v>0</v>
-      </c>
-      <c r="L21" s="39">
-        <v>0</v>
-      </c>
-      <c r="M21" s="15">
-        <v>100</v>
-      </c>
-      <c r="N21" s="14">
-        <v>99</v>
-      </c>
-      <c r="O21" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P21" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q21" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R21" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S21" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="42"/>
+      <c r="S21" s="45"/>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C22" s="16">
         <v>17</v>
       </c>
-      <c r="D22" s="6">
-        <v>24</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="5">
-        <v>0</v>
-      </c>
-      <c r="K22" s="36">
-        <v>0</v>
-      </c>
-      <c r="L22" s="39">
-        <v>0</v>
-      </c>
-      <c r="M22" s="15">
-        <v>100</v>
-      </c>
-      <c r="N22" s="14">
-        <v>99</v>
-      </c>
-      <c r="O22" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P22" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q22" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R22" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S22" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="42"/>
+      <c r="S22" s="45"/>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C23" s="16">
         <v>18</v>
       </c>
-      <c r="D23" s="6">
-        <v>24</v>
-      </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
-      <c r="J23" s="5">
-        <v>0</v>
-      </c>
-      <c r="K23" s="36">
-        <v>0</v>
-      </c>
-      <c r="L23" s="39">
-        <v>0</v>
-      </c>
-      <c r="M23" s="15">
-        <v>100</v>
-      </c>
-      <c r="N23" s="14">
-        <v>99</v>
-      </c>
-      <c r="O23" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P23" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q23" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R23" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S23" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D23" s="6"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="42"/>
+      <c r="S23" s="45"/>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C24" s="16">
         <v>19</v>
       </c>
-      <c r="D24" s="6">
-        <v>24</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="5">
-        <v>0</v>
-      </c>
-      <c r="K24" s="36">
-        <v>0</v>
-      </c>
-      <c r="L24" s="39">
-        <v>0</v>
-      </c>
-      <c r="M24" s="15">
-        <v>100</v>
-      </c>
-      <c r="N24" s="14">
-        <v>99</v>
-      </c>
-      <c r="O24" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P24" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q24" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R24" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S24" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="42"/>
+      <c r="S24" s="45"/>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C25" s="16">
         <v>20</v>
       </c>
-      <c r="D25" s="6">
-        <v>24</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3">
-        <v>0</v>
-      </c>
-      <c r="G25" s="3">
-        <v>0</v>
-      </c>
-      <c r="H25" s="3">
-        <v>0</v>
-      </c>
-      <c r="I25" s="3">
-        <v>0</v>
-      </c>
-      <c r="J25" s="5">
-        <v>0</v>
-      </c>
-      <c r="K25" s="36">
-        <v>0</v>
-      </c>
-      <c r="L25" s="39">
-        <v>0</v>
-      </c>
-      <c r="M25" s="15">
-        <v>100</v>
-      </c>
-      <c r="N25" s="14">
-        <v>99</v>
-      </c>
-      <c r="O25" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P25" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q25" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R25" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S25" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="42"/>
+      <c r="S25" s="45"/>
     </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C26" s="16">
         <v>21</v>
       </c>
-      <c r="D26" s="6">
-        <v>24</v>
-      </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5">
-        <v>0</v>
-      </c>
-      <c r="K26" s="36">
-        <v>0</v>
-      </c>
-      <c r="L26" s="39">
-        <v>0</v>
-      </c>
-      <c r="M26" s="15">
-        <v>100</v>
-      </c>
-      <c r="N26" s="14">
-        <v>99</v>
-      </c>
-      <c r="O26" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P26" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q26" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R26" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S26" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="36"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="42"/>
+      <c r="S26" s="45"/>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C27" s="16">
         <v>22</v>
       </c>
-      <c r="D27" s="6">
-        <v>24</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="5">
-        <v>0</v>
-      </c>
-      <c r="K27" s="36">
-        <v>0</v>
-      </c>
-      <c r="L27" s="39">
-        <v>0</v>
-      </c>
-      <c r="M27" s="15">
-        <v>100</v>
-      </c>
-      <c r="N27" s="14">
-        <v>99</v>
-      </c>
-      <c r="O27" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P27" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q27" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R27" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S27" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="42"/>
+      <c r="S27" s="45"/>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C28" s="16">
         <v>23</v>
       </c>
-      <c r="D28" s="6">
-        <v>24</v>
-      </c>
-      <c r="E28" s="3">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3">
-        <v>0</v>
-      </c>
-      <c r="G28" s="3">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3">
-        <v>0</v>
-      </c>
-      <c r="I28" s="3">
-        <v>0</v>
-      </c>
-      <c r="J28" s="5">
-        <v>0</v>
-      </c>
-      <c r="K28" s="36">
-        <v>0</v>
-      </c>
-      <c r="L28" s="39">
-        <v>0</v>
-      </c>
-      <c r="M28" s="15">
-        <v>100</v>
-      </c>
-      <c r="N28" s="14">
-        <v>99</v>
-      </c>
-      <c r="O28" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P28" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q28" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R28" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S28" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D28" s="6"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="42"/>
+      <c r="S28" s="45"/>
     </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C29" s="16">
         <v>24</v>
       </c>
-      <c r="D29" s="6">
-        <v>24</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="5">
-        <v>0</v>
-      </c>
-      <c r="K29" s="36">
-        <v>0</v>
-      </c>
-      <c r="L29" s="39">
-        <v>0</v>
-      </c>
-      <c r="M29" s="15">
-        <v>100</v>
-      </c>
-      <c r="N29" s="14">
-        <v>99</v>
-      </c>
-      <c r="O29" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P29" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q29" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R29" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S29" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="42"/>
+      <c r="S29" s="45"/>
     </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C30" s="16">
         <v>25</v>
       </c>
-      <c r="D30" s="6">
-        <v>24</v>
-      </c>
-      <c r="E30" s="3">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3">
-        <v>0</v>
-      </c>
-      <c r="H30" s="3">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3">
-        <v>0</v>
-      </c>
-      <c r="J30" s="5">
-        <v>0</v>
-      </c>
-      <c r="K30" s="36">
-        <v>0</v>
-      </c>
-      <c r="L30" s="39">
-        <v>0</v>
-      </c>
-      <c r="M30" s="15">
-        <v>100</v>
-      </c>
-      <c r="N30" s="14">
-        <v>99</v>
-      </c>
-      <c r="O30" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P30" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q30" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R30" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S30" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="42"/>
+      <c r="S30" s="45"/>
     </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C31" s="16">
         <v>26</v>
       </c>
-      <c r="D31" s="6">
-        <v>24</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3">
-        <v>0</v>
-      </c>
-      <c r="G31" s="3">
-        <v>0</v>
-      </c>
-      <c r="H31" s="3">
-        <v>0</v>
-      </c>
-      <c r="I31" s="3">
-        <v>0</v>
-      </c>
-      <c r="J31" s="5">
-        <v>0</v>
-      </c>
-      <c r="K31" s="36">
-        <v>0</v>
-      </c>
-      <c r="L31" s="39">
-        <v>0</v>
-      </c>
-      <c r="M31" s="15">
-        <v>100</v>
-      </c>
-      <c r="N31" s="14">
-        <v>99</v>
-      </c>
-      <c r="O31" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P31" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q31" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R31" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S31" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D31" s="6"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="42"/>
+      <c r="S31" s="45"/>
     </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C32" s="16">
         <v>27</v>
       </c>
-      <c r="D32" s="6">
-        <v>24</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="5">
-        <v>0</v>
-      </c>
-      <c r="K32" s="36">
-        <v>0</v>
-      </c>
-      <c r="L32" s="39">
-        <v>0</v>
-      </c>
-      <c r="M32" s="15">
-        <v>100</v>
-      </c>
-      <c r="N32" s="14">
-        <v>99</v>
-      </c>
-      <c r="O32" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P32" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q32" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R32" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S32" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
-      <c r="AA32" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="D32" s="6"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="39"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="4"/>
+      <c r="R32" s="42"/>
+      <c r="S32" s="45"/>
     </row>
     <row r="33" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C33" s="16">
         <v>28</v>
       </c>
-      <c r="D33" s="6">
-        <v>24</v>
-      </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
-      <c r="J33" s="5">
-        <v>0</v>
-      </c>
-      <c r="K33" s="36">
-        <v>0</v>
-      </c>
-      <c r="L33" s="39">
-        <v>0</v>
-      </c>
-      <c r="M33" s="15">
-        <v>100</v>
-      </c>
-      <c r="N33" s="14">
-        <v>99</v>
-      </c>
-      <c r="O33" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P33" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q33" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R33" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S33" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D33" s="6"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="36"/>
+      <c r="L33" s="39"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="42"/>
+      <c r="S33" s="45"/>
     </row>
     <row r="34" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C34" s="16">
         <v>29</v>
       </c>
-      <c r="D34" s="6">
-        <v>24</v>
-      </c>
-      <c r="E34" s="3">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3">
-        <v>0</v>
-      </c>
-      <c r="G34" s="3">
-        <v>0</v>
-      </c>
-      <c r="H34" s="3">
-        <v>0</v>
-      </c>
-      <c r="I34" s="3">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5">
-        <v>0</v>
-      </c>
-      <c r="K34" s="36">
-        <v>0</v>
-      </c>
-      <c r="L34" s="39">
-        <v>0</v>
-      </c>
-      <c r="M34" s="15">
-        <v>100</v>
-      </c>
-      <c r="N34" s="14">
-        <v>99</v>
-      </c>
-      <c r="O34" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P34" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q34" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R34" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S34" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D34" s="6"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="42"/>
+      <c r="S34" s="45"/>
     </row>
     <row r="35" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C35" s="16">
         <v>30</v>
       </c>
-      <c r="D35" s="6">
-        <v>24</v>
-      </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
-      <c r="J35" s="5">
-        <v>0</v>
-      </c>
-      <c r="K35" s="36">
-        <v>0</v>
-      </c>
-      <c r="L35" s="39">
-        <v>0</v>
-      </c>
-      <c r="M35" s="15">
-        <v>100</v>
-      </c>
-      <c r="N35" s="14">
-        <v>99</v>
-      </c>
-      <c r="O35" s="5">
-        <v>95.5</v>
-      </c>
-      <c r="P35" s="15">
-        <v>34.567</v>
-      </c>
-      <c r="Q35" s="4">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R35" s="42">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S35" s="45">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D35" s="6"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="36"/>
+      <c r="L35" s="39"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="42"/>
+      <c r="S35" s="45"/>
     </row>
     <row r="36" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C36" s="30">
         <v>31</v>
       </c>
-      <c r="D36" s="10">
-        <v>24</v>
-      </c>
-      <c r="E36" s="11">
-        <v>0</v>
-      </c>
-      <c r="F36" s="11">
-        <v>0</v>
-      </c>
-      <c r="G36" s="11">
-        <v>0</v>
-      </c>
-      <c r="H36" s="11">
-        <v>0</v>
-      </c>
-      <c r="I36" s="11">
-        <v>0</v>
-      </c>
-      <c r="J36" s="12">
-        <v>0</v>
-      </c>
-      <c r="K36" s="37">
-        <v>0</v>
-      </c>
-      <c r="L36" s="40">
-        <v>0</v>
-      </c>
-      <c r="M36" s="31">
-        <v>100</v>
-      </c>
-      <c r="N36" s="32">
-        <v>99</v>
-      </c>
-      <c r="O36" s="12">
-        <v>95.5</v>
-      </c>
-      <c r="P36" s="31">
-        <v>34.567</v>
-      </c>
-      <c r="Q36" s="33">
-        <v>31.455970000000001</v>
-      </c>
-      <c r="R36" s="43">
-        <f t="shared" si="0"/>
-        <v>3.1110299999999995</v>
-      </c>
-      <c r="S36" s="46">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
+      <c r="D36" s="10"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="37"/>
+      <c r="L36" s="40"/>
+      <c r="M36" s="31"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="12"/>
+      <c r="P36" s="31"/>
+      <c r="Q36" s="33"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="46"/>
     </row>
     <row r="37" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C37" s="48" t="s">
@@ -6778,31 +5284,31 @@
       </c>
       <c r="D37" s="49">
         <f>SUM(D6:D36)</f>
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="E37" s="50">
-        <f t="shared" ref="E37:J37" si="2">SUM(E6:E36)</f>
-        <v>24</v>
+        <f t="shared" ref="E37:J37" si="0">SUM(E6:E36)</f>
+        <v>0</v>
       </c>
       <c r="F37" s="50">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G37" s="50">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H37" s="50">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="I37" s="50">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="J37" s="51">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K37" s="52">
         <f>SUM(K6:K36)</f>
@@ -6814,148 +5320,77 @@
       </c>
       <c r="M37" s="54">
         <f>MAX(M6:M36)</f>
-        <v>100</v>
-      </c>
-      <c r="N37" s="53">
+        <v>0</v>
+      </c>
+      <c r="N37" s="53" t="e">
         <f>AVERAGE(N6:N36)</f>
-        <v>99</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O37" s="51">
         <f>MIN(O6:O36)</f>
-        <v>95.5</v>
+        <v>0</v>
       </c>
       <c r="P37" s="27">
-        <f t="shared" ref="P37" si="3">SUM(P6:P36)</f>
-        <v>1071.577</v>
+        <f t="shared" ref="P37" si="1">SUM(P6:P36)</f>
+        <v>0</v>
       </c>
       <c r="Q37" s="28">
-        <f t="shared" ref="Q37" si="4">SUM(Q6:Q36)</f>
-        <v>975.13506999999959</v>
+        <f t="shared" ref="Q37" si="2">SUM(Q6:Q36)</f>
+        <v>0</v>
       </c>
       <c r="R37" s="29">
-        <f t="shared" ref="R37" si="5">SUM(R6:R36)</f>
-        <v>96.441929999999985</v>
-      </c>
-      <c r="S37" s="55">
-        <f t="shared" si="1"/>
-        <v>90.999999999999957</v>
+        <f t="shared" ref="R37" si="3">SUM(R6:R36)</f>
+        <v>0</v>
+      </c>
+      <c r="S37" s="55" t="e">
+        <f>Q37/P37*100</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="38" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C38" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E38" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="F38" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="H38" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="J38" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="K38" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L38" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="M38" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="N38" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="O38" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="P38" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q38" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="R38" s="58" t="s">
-        <v>15</v>
-      </c>
-      <c r="S38" s="34" t="s">
-        <v>15</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="D38" s="27"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="27"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="27"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="56"/>
+      <c r="Q38" s="57"/>
+      <c r="R38" s="58"/>
+      <c r="S38" s="34"/>
     </row>
     <row r="39" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C39" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E39" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="F39" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="J39" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="K39" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L39" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="M39" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="N39" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="O39" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="P39" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q39" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="R39" s="58" t="s">
-        <v>15</v>
-      </c>
-      <c r="S39" s="34" t="s">
-        <v>15</v>
-      </c>
+      <c r="D39" s="27"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="27"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="27"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="29"/>
+      <c r="P39" s="56"/>
+      <c r="Q39" s="57"/>
+      <c r="R39" s="58"/>
+      <c r="S39" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C3:S3"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="K4:L4"/>
     <mergeCell ref="T3:AC3"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
@@ -6967,6 +5402,13 @@
     <mergeCell ref="AA4:AA5"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="AC4:AC5"/>
+    <mergeCell ref="C3:S3"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="K4:L4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/report/MonthReport.xlsx
+++ b/public/report/MonthReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\test\SEEMS_EMS\public\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58CF1F9-82D4-47D6-98D0-EA260C54C97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACF489D-E73C-45B7-B94B-AC4CB0B6609D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="735" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月報" sheetId="1" r:id="rId1"/>
@@ -42,21 +42,9 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={81E50B7B-3969-4832-B952-3EF905E0C831}</author>
-    <author>tc={FCB8E4AE-9350-453E-807E-C9E28EA2FE77}</author>
   </authors>
   <commentList>
     <comment ref="C3" authorId="0" shapeId="0" xr:uid="{81E50B7B-3969-4832-B952-3EF905E0C831}">
-      <text>
-        <t>[對話串註解]
-您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
-註解:
-    XX=縣市
-YY=地區
-ZZ=併網容量
-e.g. 花蓮和平10MW</t>
-      </text>
-    </comment>
-    <comment ref="T3" authorId="1" shapeId="0" xr:uid="{FCB8E4AE-9350-453E-807E-C9E28EA2FE77}">
       <text>
         <t>[對話串註解]
 您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
@@ -72,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>日
 (Day)</t>
@@ -140,88 +128,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>XXYYZZ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve">MW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>E-dReg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>AA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>BB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>月 月報</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>本期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -271,6 +177,18 @@
 (kWh)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>花蓮和平10MW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E-dReg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月報</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -280,7 +198,7 @@
     <numFmt numFmtId="176" formatCode="0.0_ "/>
     <numFmt numFmtId="177" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,19 +227,6 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -331,7 +236,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="46">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -599,44 +504,7 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -878,19 +746,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -933,6 +788,76 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -990,11 +915,181 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1002,201 +1097,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -4406,12 +4321,6 @@
 ZZ=併網容量
 e.g. 花蓮和平10MW</text>
   </threadedComment>
-  <threadedComment ref="T3" dT="2023-11-27T08:34:48.63" personId="{B8A74333-F443-456F-BDB7-E92946D76E41}" id="{FCB8E4AE-9350-453E-807E-C9E28EA2FE77}">
-    <text>XX=縣市
-YY=地區
-ZZ=併網容量
-e.g. 花蓮和平10MW</text>
-  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -4437,103 +4346,123 @@
     <col min="30" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:29" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="61" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="73" t="s">
-        <v>16</v>
-      </c>
-      <c r="U3" s="74"/>
-      <c r="V3" s="74"/>
-      <c r="W3" s="74"/>
-      <c r="X3" s="74"/>
-      <c r="Y3" s="74"/>
-      <c r="Z3" s="74"/>
-      <c r="AA3" s="74"/>
-      <c r="AB3" s="74"/>
-      <c r="AC3" s="75"/>
+    <row r="2" spans="3:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="74"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="74"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="74"/>
+    </row>
+    <row r="3" spans="3:29" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="82"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="83" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="83"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="83"/>
+      <c r="S3" s="84"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="72"/>
+      <c r="V3" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="83"/>
+      <c r="X3" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y3" s="73"/>
+      <c r="Z3" s="73"/>
+      <c r="AA3" s="83" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB3" s="83"/>
+      <c r="AC3" s="84"/>
     </row>
     <row r="4" spans="3:29" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="67" t="s">
+      <c r="C4" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="D4" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="67" t="s">
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="78"/>
+      <c r="K4" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="71"/>
-      <c r="M4" s="67" t="s">
+      <c r="L4" s="79"/>
+      <c r="M4" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="71"/>
-      <c r="O4" s="72"/>
-      <c r="P4" s="67" t="s">
+      <c r="N4" s="79"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="71"/>
-      <c r="S4" s="69" t="s">
+      <c r="Q4" s="79"/>
+      <c r="R4" s="79"/>
+      <c r="S4" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="T4" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="U4" s="78" t="s">
+      <c r="T4" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="U4" s="63" t="s">
+        <v>18</v>
+      </c>
+      <c r="V4" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="V4" s="80" t="s">
+      <c r="W4" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="W4" s="80" t="s">
+      <c r="X4" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="X4" s="82" t="s">
+      <c r="Y4" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="Y4" s="80" t="s">
+      <c r="Z4" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="Z4" s="82" t="s">
+      <c r="AA4" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="AA4" s="80" t="s">
+      <c r="AB4" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="AB4" s="82" t="s">
+      <c r="AC4" s="68" t="s">
         <v>26</v>
-      </c>
-      <c r="AC4" s="83" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" spans="3:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="68"/>
+      <c r="C5" s="70"/>
       <c r="D5" s="7">
         <v>1</v>
       </c>
@@ -4579,17 +4508,17 @@
       <c r="R5" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="S5" s="70"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="79"/>
-      <c r="V5" s="81"/>
-      <c r="W5" s="81"/>
-      <c r="X5" s="81"/>
-      <c r="Y5" s="81"/>
-      <c r="Z5" s="81"/>
-      <c r="AA5" s="81"/>
-      <c r="AB5" s="81"/>
-      <c r="AC5" s="84"/>
+      <c r="S5" s="71"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="64"/>
+      <c r="V5" s="66"/>
+      <c r="W5" s="66"/>
+      <c r="X5" s="66"/>
+      <c r="Y5" s="66"/>
+      <c r="Z5" s="66"/>
+      <c r="AA5" s="66"/>
+      <c r="AB5" s="66"/>
+      <c r="AC5" s="69"/>
     </row>
     <row r="6" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C6" s="17">
@@ -4612,7 +4541,7 @@
       <c r="R6" s="41"/>
       <c r="S6" s="44"/>
       <c r="T6" s="60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
@@ -4645,7 +4574,7 @@
       <c r="R7" s="42"/>
       <c r="S7" s="45"/>
       <c r="T7" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
@@ -5349,7 +5278,7 @@
     </row>
     <row r="38" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C38" s="34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="28"/>
@@ -5391,7 +5320,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="T3:AC3"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="K3:M3"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
     <mergeCell ref="V4:V5"/>
@@ -5402,13 +5337,7 @@
     <mergeCell ref="AA4:AA5"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="AC4:AC5"/>
-    <mergeCell ref="C3:S3"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="Y3:Z3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/report/MonthReport.xlsx
+++ b/public/report/MonthReport.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\test\SEEMS_EMS\public\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACF489D-E73C-45B7-B94B-AC4CB0B6609D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1322E485-43EC-42A5-A247-50CB212C9CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="735" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="月報" sheetId="1" r:id="rId1"/>
+    <sheet name="圖表" sheetId="3" r:id="rId1"/>
+    <sheet name="數值" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">月報!$C$3:$AC$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">圖表!$C$3:$L$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">數值!$C$3:$S$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -870,7 +872,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1050,6 +1052,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1062,56 +1086,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1225,11 +1226,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-78B1-4AAA-BFBB-F64C9B27CBA4}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1245,11 +1241,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-78B1-4AAA-BFBB-F64C9B27CBA4}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1265,11 +1256,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-78B1-4AAA-BFBB-F64C9B27CBA4}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1285,11 +1271,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-78B1-4AAA-BFBB-F64C9B27CBA4}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1305,11 +1286,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-78B1-4AAA-BFBB-F64C9B27CBA4}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1325,11 +1301,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-78B1-4AAA-BFBB-F64C9B27CBA4}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1347,11 +1318,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-78B1-4AAA-BFBB-F64C9B27CBA4}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -1369,15 +1335,10 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-B53F-4EAD-B8FC-1524B3AA546F}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:numRef>
-              <c:f>月報!$D$5:$J$5</c:f>
+              <c:f>數值!$D$5:$J$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1407,37 +1368,16 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>月報!$D$37:$J$37</c:f>
+              <c:f>數值!$D$37:$J$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-30CB-4D3E-97DA-65707377126D}"/>
+              <c16:uniqueId val="{00000020-BF5F-4138-96C4-0D582F0C795F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1683,6 +1623,14 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>數值!$S$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent2"/>
@@ -1696,16 +1644,16 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>月報!$S$6:$S$36</c:f>
+              <c:f>數值!$S$7:$S$36</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="30"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2495-440E-816A-9A6565216968}"/>
+              <c16:uniqueId val="{00000000-E34C-4960-873D-03C8BAFF5CCB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2005,18 +1953,7 @@
           <c:idx val="2"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>月報!$O$4:$O$5</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>SPM (%)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Min.</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>SPM (%) Min.</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -2031,7 +1968,7 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>月報!$O$6:$O$36</c:f>
+              <c:f>數值!$O$6:$O$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
@@ -2040,7 +1977,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-0359-4B47-B3C0-EFD6BCFBAF00}"/>
+              <c16:uniqueId val="{00000002-BCC1-4121-A94D-2F0DE3B9A462}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2048,18 +1985,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:strRef>
-              <c:f>月報!$N$4:$N$5</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>SPM (%)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Avg.</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>SPM (%) Avg.</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -2074,7 +2000,7 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>月報!$N$6:$N$36</c:f>
+              <c:f>數值!$N$6:$N$36</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="31"/>
@@ -2083,7 +2009,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0359-4B47-B3C0-EFD6BCFBAF00}"/>
+              <c16:uniqueId val="{00000001-BCC1-4121-A94D-2F0DE3B9A462}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2091,18 +2017,7 @@
           <c:idx val="0"/>
           <c:order val="2"/>
           <c:tx>
-            <c:strRef>
-              <c:f>月報!$M$4:$M$5</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>SPM (%)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Max.</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>SPM (%) Max.</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -2117,7 +2032,7 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>月報!$M$6:$M$36</c:f>
+              <c:f>數值!$M$6:$M$36</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="31"/>
@@ -2126,7 +2041,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0359-4B47-B3C0-EFD6BCFBAF00}"/>
+              <c16:uniqueId val="{00000000-BCC1-4121-A94D-2F0DE3B9A462}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2151,6 +2066,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3937,13 +3853,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>27495</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>171191</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>745791</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>23171</xdr:rowOff>
@@ -3953,11 +3869,13 @@
         <xdr:cNvPr id="2" name="圖表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F72ED16-3DF4-8DFE-25D4-155CDDC59049}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27EAE1C2-4974-4CDD-AFEF-02F79EF7409B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -3973,13 +3891,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>19602</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>165783</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>817142</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>10187</xdr:rowOff>
@@ -3989,11 +3907,13 @@
         <xdr:cNvPr id="3" name="圖表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE5E11AC-7173-E330-BE9F-FC23544C3DA4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A428A67D-5634-4B0F-81EA-79787DC97992}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4009,13 +3929,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>20995</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>15903</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>751058</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>157370</xdr:rowOff>
@@ -4025,11 +3945,13 @@
         <xdr:cNvPr id="4" name="圖表 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BA2FD57-B091-4BED-754A-FBAE68392853}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81B24196-EF9B-493B-9C5E-B4DE9286FF97}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4325,11 +4247,151 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C771C0EC-A1E9-455B-BD62-B2A2400E08E8}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="C2:L8"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="8.75" style="1"/>
+    <col min="3" max="3" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="14" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.75" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:12" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="62"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="61" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="61"/>
+      <c r="L3" s="63"/>
+    </row>
+    <row r="4" spans="3:12" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="71" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="65" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="69" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="67" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C5" s="72"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="68"/>
+    </row>
+    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C6" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="5"/>
+    </row>
+    <row r="8" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="64"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="96" fitToWidth="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="C2:AC39"/>
+  <dimension ref="C2:S39"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.75" style="1"/>
@@ -4341,128 +4403,71 @@
     <col min="15" max="15" width="7.5" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
     <col min="19" max="19" width="12.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="29" width="14" style="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.75" style="1"/>
+    <col min="20" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="74"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="74"/>
+    <row r="2" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J2" s="1"/>
+      <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="3:29" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="82"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="72" t="s">
+    <row r="3" spans="3:19" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="62"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="72" t="s">
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73"/>
-      <c r="N3" s="83" t="s">
+      <c r="K3" s="70"/>
+      <c r="L3" s="70"/>
+      <c r="M3" s="70"/>
+      <c r="N3" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="84"/>
-      <c r="T3" s="82"/>
-      <c r="U3" s="72"/>
-      <c r="V3" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="W3" s="83"/>
-      <c r="X3" s="72" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y3" s="73"/>
-      <c r="Z3" s="73"/>
-      <c r="AA3" s="83" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB3" s="83"/>
-      <c r="AC3" s="84"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="61"/>
+      <c r="R3" s="61"/>
+      <c r="S3" s="63"/>
     </row>
-    <row r="4" spans="3:29" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="75" t="s">
+    <row r="4" spans="3:19" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="76" t="s">
+      <c r="D4" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="75" t="s">
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="79"/>
-      <c r="M4" s="75" t="s">
+      <c r="L4" s="82"/>
+      <c r="M4" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="79"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="75" t="s">
+      <c r="N4" s="82"/>
+      <c r="O4" s="83"/>
+      <c r="P4" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="79"/>
-      <c r="S4" s="81" t="s">
+      <c r="Q4" s="82"/>
+      <c r="R4" s="82"/>
+      <c r="S4" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="T4" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="U4" s="63" t="s">
-        <v>18</v>
-      </c>
-      <c r="V4" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="W4" s="65" t="s">
-        <v>20</v>
-      </c>
-      <c r="X4" s="67" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y4" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z4" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA4" s="65" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB4" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC4" s="68" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="5" spans="3:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="70"/>
+    <row r="5" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="79"/>
       <c r="D5" s="7">
         <v>1</v>
       </c>
@@ -4508,19 +4513,9 @@
       <c r="R5" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="S5" s="71"/>
-      <c r="T5" s="62"/>
-      <c r="U5" s="64"/>
-      <c r="V5" s="66"/>
-      <c r="W5" s="66"/>
-      <c r="X5" s="66"/>
-      <c r="Y5" s="66"/>
-      <c r="Z5" s="66"/>
-      <c r="AA5" s="66"/>
-      <c r="AB5" s="66"/>
-      <c r="AC5" s="69"/>
+      <c r="S5" s="81"/>
     </row>
-    <row r="6" spans="3:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C6" s="17">
         <v>1</v>
       </c>
@@ -4540,20 +4535,8 @@
       <c r="Q6" s="26"/>
       <c r="R6" s="41"/>
       <c r="S6" s="44"/>
-      <c r="T6" s="60" t="s">
-        <v>16</v>
-      </c>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="5"/>
     </row>
-    <row r="7" spans="3:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C7" s="16">
         <v>2</v>
       </c>
@@ -4573,20 +4556,8 @@
       <c r="Q7" s="4"/>
       <c r="R7" s="42"/>
       <c r="S7" s="45"/>
-      <c r="T7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="5"/>
     </row>
-    <row r="8" spans="3:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C8" s="16">
         <v>3</v>
       </c>
@@ -4606,20 +4577,8 @@
       <c r="Q8" s="4"/>
       <c r="R8" s="42"/>
       <c r="S8" s="45"/>
-      <c r="T8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="9"/>
     </row>
-    <row r="9" spans="3:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C9" s="16">
         <v>4</v>
       </c>
@@ -4640,7 +4599,7 @@
       <c r="R9" s="42"/>
       <c r="S9" s="45"/>
     </row>
-    <row r="10" spans="3:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C10" s="16">
         <v>5</v>
       </c>
@@ -4661,7 +4620,7 @@
       <c r="R10" s="42"/>
       <c r="S10" s="45"/>
     </row>
-    <row r="11" spans="3:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C11" s="16">
         <v>6</v>
       </c>
@@ -4682,7 +4641,7 @@
       <c r="R11" s="42"/>
       <c r="S11" s="45"/>
     </row>
-    <row r="12" spans="3:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C12" s="16">
         <v>7</v>
       </c>
@@ -4703,7 +4662,7 @@
       <c r="R12" s="42"/>
       <c r="S12" s="45"/>
     </row>
-    <row r="13" spans="3:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C13" s="16">
         <v>8</v>
       </c>
@@ -4724,7 +4683,7 @@
       <c r="R13" s="42"/>
       <c r="S13" s="45"/>
     </row>
-    <row r="14" spans="3:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C14" s="16">
         <v>9</v>
       </c>
@@ -4745,7 +4704,7 @@
       <c r="R14" s="42"/>
       <c r="S14" s="45"/>
     </row>
-    <row r="15" spans="3:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C15" s="16">
         <v>10</v>
       </c>
@@ -4766,7 +4725,7 @@
       <c r="R15" s="42"/>
       <c r="S15" s="45"/>
     </row>
-    <row r="16" spans="3:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C16" s="16">
         <v>11</v>
       </c>
@@ -5211,70 +5170,22 @@
       <c r="C37" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="49">
-        <f>SUM(D6:D36)</f>
-        <v>0</v>
-      </c>
-      <c r="E37" s="50">
-        <f t="shared" ref="E37:J37" si="0">SUM(E6:E36)</f>
-        <v>0</v>
-      </c>
-      <c r="F37" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G37" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J37" s="51">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K37" s="52">
-        <f>SUM(K6:K36)</f>
-        <v>0</v>
-      </c>
-      <c r="L37" s="59">
-        <f>SUM(L6:L36)</f>
-        <v>0</v>
-      </c>
-      <c r="M37" s="54">
-        <f>MAX(M6:M36)</f>
-        <v>0</v>
-      </c>
-      <c r="N37" s="53" t="e">
-        <f>AVERAGE(N6:N36)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O37" s="51">
-        <f>MIN(O6:O36)</f>
-        <v>0</v>
-      </c>
-      <c r="P37" s="27">
-        <f t="shared" ref="P37" si="1">SUM(P6:P36)</f>
-        <v>0</v>
-      </c>
-      <c r="Q37" s="28">
-        <f t="shared" ref="Q37" si="2">SUM(Q6:Q36)</f>
-        <v>0</v>
-      </c>
-      <c r="R37" s="29">
-        <f t="shared" ref="R37" si="3">SUM(R6:R36)</f>
-        <v>0</v>
-      </c>
-      <c r="S37" s="55" t="e">
-        <f>Q37/P37*100</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="D37" s="49"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="50"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="51"/>
+      <c r="K37" s="52"/>
+      <c r="L37" s="59"/>
+      <c r="M37" s="54"/>
+      <c r="N37" s="53"/>
+      <c r="O37" s="51"/>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="55"/>
     </row>
     <row r="38" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C38" s="34" t="s">
@@ -5319,33 +5230,18 @@
       <c r="S39" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="7">
+    <mergeCell ref="K3:M3"/>
     <mergeCell ref="D4:J4"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="S4:S5"/>
     <mergeCell ref="M4:O4"/>
     <mergeCell ref="P4:R4"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="Y4:Y5"/>
-    <mergeCell ref="Z4:Z5"/>
-    <mergeCell ref="AA4:AA5"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="AC4:AC5"/>
-    <mergeCell ref="Y3:Z3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="95" fitToWidth="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="D37:J37" formulaRange="1"/>
-  </ignoredErrors>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/public/report/MonthReport.xlsx
+++ b/public/report/MonthReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\test\SEEMS_EMS\public\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1322E485-43EC-42A5-A247-50CB212C9CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF5A07C-7D24-41E9-973C-48C76CB6B2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="735" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -238,7 +238,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="48">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -842,7 +842,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -856,10 +858,34 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -872,7 +898,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1056,6 +1082,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1071,21 +1112,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1101,16 +1127,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1226,6 +1258,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-013F-4545-995A-7445E08A7F69}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1241,6 +1278,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-013F-4545-995A-7445E08A7F69}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1256,6 +1298,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-013F-4545-995A-7445E08A7F69}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1271,6 +1318,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-013F-4545-995A-7445E08A7F69}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1286,6 +1338,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-013F-4545-995A-7445E08A7F69}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1301,6 +1358,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-013F-4545-995A-7445E08A7F69}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1318,6 +1380,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-013F-4545-995A-7445E08A7F69}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -1335,6 +1402,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-013F-4545-995A-7445E08A7F69}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:numRef>
@@ -1968,7 +2040,7 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>數值!$O$6:$O$36</c:f>
+              <c:f>數值!$M$6:$M$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
@@ -2000,7 +2072,7 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>數值!$N$6:$N$36</c:f>
+              <c:f>數值!$L$6:$L$36</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="31"/>
@@ -2032,7 +2104,7 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>數值!$M$6:$M$36</c:f>
+              <c:f>數值!$K$6:$K$36</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="31"/>
@@ -4271,8 +4343,8 @@
       <c r="G3" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
       <c r="J3" s="61" t="s">
         <v>30</v>
       </c>
@@ -4280,48 +4352,48 @@
       <c r="L3" s="63"/>
     </row>
     <row r="4" spans="3:12" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="73" t="s">
+      <c r="D4" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="69" t="s">
+      <c r="E4" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="69" t="s">
+      <c r="F4" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="69" t="s">
+      <c r="H4" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="65" t="s">
+      <c r="I4" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="69" t="s">
+      <c r="J4" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="65" t="s">
+      <c r="K4" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="67" t="s">
+      <c r="L4" s="72" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C5" s="72"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="66"/>
-      <c r="L5" s="68"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="73"/>
     </row>
     <row r="6" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C6" s="60" t="s">
@@ -4423,9 +4495,9 @@
       <c r="J3" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
       <c r="N3" s="61" t="s">
         <v>30</v>
       </c>
@@ -4448,19 +4520,19 @@
       <c r="H4" s="76"/>
       <c r="I4" s="76"/>
       <c r="J4" s="77"/>
-      <c r="K4" s="78" t="s">
+      <c r="K4" s="83" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="84"/>
+      <c r="M4" s="85"/>
+      <c r="N4" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="84"/>
+      <c r="P4" s="85"/>
+      <c r="Q4" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="82"/>
-      <c r="M4" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="N4" s="82"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q4" s="82"/>
       <c r="R4" s="82"/>
       <c r="S4" s="80" t="s">
         <v>1</v>
@@ -4490,28 +4562,28 @@
         <v>-1</v>
       </c>
       <c r="K5" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="M5" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="O5" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="P5" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q5" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="23" t="s">
+      <c r="R5" s="23" t="s">
         <v>13</v>
-      </c>
-      <c r="M5" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="N5" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="P5" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q5" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="R5" s="47" t="s">
-        <v>8</v>
       </c>
       <c r="S5" s="81"/>
     </row>
@@ -4526,14 +4598,14 @@
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
       <c r="J6" s="13"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="26"/>
-      <c r="R6" s="41"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="38"/>
       <c r="S6" s="44"/>
     </row>
     <row r="7" spans="3:19" x14ac:dyDescent="0.3">
@@ -4547,14 +4619,14 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="5"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="42"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="39"/>
       <c r="S7" s="45"/>
     </row>
     <row r="8" spans="3:19" x14ac:dyDescent="0.3">
@@ -4568,14 +4640,14 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="5"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="42"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="39"/>
       <c r="S8" s="45"/>
     </row>
     <row r="9" spans="3:19" x14ac:dyDescent="0.3">
@@ -4589,14 +4661,14 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="5"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="42"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="42"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="39"/>
       <c r="S9" s="45"/>
     </row>
     <row r="10" spans="3:19" x14ac:dyDescent="0.3">
@@ -4610,14 +4682,14 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="5"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="42"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="42"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="39"/>
       <c r="S10" s="45"/>
     </row>
     <row r="11" spans="3:19" x14ac:dyDescent="0.3">
@@ -4631,14 +4703,14 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="5"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="42"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="39"/>
       <c r="S11" s="45"/>
     </row>
     <row r="12" spans="3:19" x14ac:dyDescent="0.3">
@@ -4652,14 +4724,14 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="5"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="42"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="39"/>
       <c r="S12" s="45"/>
     </row>
     <row r="13" spans="3:19" x14ac:dyDescent="0.3">
@@ -4673,14 +4745,14 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="5"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="42"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="39"/>
       <c r="S13" s="45"/>
     </row>
     <row r="14" spans="3:19" x14ac:dyDescent="0.3">
@@ -4694,14 +4766,14 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="5"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="42"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="39"/>
       <c r="S14" s="45"/>
     </row>
     <row r="15" spans="3:19" x14ac:dyDescent="0.3">
@@ -4715,14 +4787,14 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="5"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="42"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="39"/>
       <c r="S15" s="45"/>
     </row>
     <row r="16" spans="3:19" x14ac:dyDescent="0.3">
@@ -4736,14 +4808,14 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="5"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="42"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="39"/>
       <c r="S16" s="45"/>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.3">
@@ -4757,14 +4829,14 @@
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="5"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="42"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="39"/>
       <c r="S17" s="45"/>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.3">
@@ -4778,14 +4850,14 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="5"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="42"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="39"/>
       <c r="S18" s="45"/>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.3">
@@ -4799,14 +4871,14 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="5"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="42"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="39"/>
       <c r="S19" s="45"/>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.3">
@@ -4820,14 +4892,14 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="5"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="42"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="39"/>
       <c r="S20" s="45"/>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.3">
@@ -4841,14 +4913,14 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="5"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="42"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="39"/>
       <c r="S21" s="45"/>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.3">
@@ -4862,14 +4934,14 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="5"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="42"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="39"/>
       <c r="S22" s="45"/>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.3">
@@ -4883,14 +4955,14 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="5"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="42"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="36"/>
+      <c r="R23" s="39"/>
       <c r="S23" s="45"/>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.3">
@@ -4904,14 +4976,14 @@
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="5"/>
-      <c r="K24" s="36"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="42"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="39"/>
       <c r="S24" s="45"/>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.3">
@@ -4925,14 +4997,14 @@
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="5"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="42"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="36"/>
+      <c r="R25" s="39"/>
       <c r="S25" s="45"/>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.3">
@@ -4946,14 +5018,14 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="5"/>
-      <c r="K26" s="36"/>
-      <c r="L26" s="39"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="42"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="36"/>
+      <c r="R26" s="39"/>
       <c r="S26" s="45"/>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.3">
@@ -4967,14 +5039,14 @@
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="5"/>
-      <c r="K27" s="36"/>
-      <c r="L27" s="39"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="42"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="36"/>
+      <c r="R27" s="39"/>
       <c r="S27" s="45"/>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.3">
@@ -4988,14 +5060,14 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="5"/>
-      <c r="K28" s="36"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="42"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="36"/>
+      <c r="R28" s="39"/>
       <c r="S28" s="45"/>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.3">
@@ -5009,14 +5081,14 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="5"/>
-      <c r="K29" s="36"/>
-      <c r="L29" s="39"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="42"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="36"/>
+      <c r="R29" s="39"/>
       <c r="S29" s="45"/>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.3">
@@ -5030,14 +5102,14 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="5"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="39"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="42"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="36"/>
+      <c r="R30" s="39"/>
       <c r="S30" s="45"/>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.3">
@@ -5051,14 +5123,14 @@
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="5"/>
-      <c r="K31" s="36"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="42"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="36"/>
+      <c r="R31" s="39"/>
       <c r="S31" s="45"/>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.3">
@@ -5072,14 +5144,14 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="5"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="39"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="42"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="36"/>
+      <c r="R32" s="39"/>
       <c r="S32" s="45"/>
     </row>
     <row r="33" spans="3:19" x14ac:dyDescent="0.3">
@@ -5093,14 +5165,14 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="5"/>
-      <c r="K33" s="36"/>
-      <c r="L33" s="39"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="42"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="36"/>
+      <c r="R33" s="39"/>
       <c r="S33" s="45"/>
     </row>
     <row r="34" spans="3:19" x14ac:dyDescent="0.3">
@@ -5114,14 +5186,14 @@
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="5"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="39"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="5"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="42"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="36"/>
+      <c r="R34" s="39"/>
       <c r="S34" s="45"/>
     </row>
     <row r="35" spans="3:19" x14ac:dyDescent="0.3">
@@ -5135,14 +5207,14 @@
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="5"/>
-      <c r="K35" s="36"/>
-      <c r="L35" s="39"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="42"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="36"/>
+      <c r="R35" s="39"/>
       <c r="S35" s="45"/>
     </row>
     <row r="36" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5156,14 +5228,14 @@
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
       <c r="J36" s="12"/>
-      <c r="K36" s="37"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="31"/>
-      <c r="N36" s="32"/>
-      <c r="O36" s="12"/>
-      <c r="P36" s="31"/>
-      <c r="Q36" s="33"/>
-      <c r="R36" s="43"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="31"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="43"/>
+      <c r="Q36" s="37"/>
+      <c r="R36" s="40"/>
       <c r="S36" s="46"/>
     </row>
     <row r="37" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5177,14 +5249,14 @@
       <c r="H37" s="50"/>
       <c r="I37" s="50"/>
       <c r="J37" s="51"/>
-      <c r="K37" s="52"/>
-      <c r="L37" s="59"/>
-      <c r="M37" s="54"/>
-      <c r="N37" s="53"/>
-      <c r="O37" s="51"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="29"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="51"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="52"/>
+      <c r="R37" s="59"/>
       <c r="S37" s="55"/>
     </row>
     <row r="38" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5199,13 +5271,13 @@
       <c r="I38" s="28"/>
       <c r="J38" s="29"/>
       <c r="K38" s="27"/>
-      <c r="L38" s="29"/>
-      <c r="M38" s="27"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="29"/>
-      <c r="P38" s="56"/>
-      <c r="Q38" s="57"/>
-      <c r="R38" s="58"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="56"/>
+      <c r="O38" s="57"/>
+      <c r="P38" s="58"/>
+      <c r="Q38" s="27"/>
+      <c r="R38" s="29"/>
       <c r="S38" s="34"/>
     </row>
     <row r="39" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5220,13 +5292,13 @@
       <c r="I39" s="28"/>
       <c r="J39" s="29"/>
       <c r="K39" s="27"/>
-      <c r="L39" s="29"/>
-      <c r="M39" s="27"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="29"/>
-      <c r="P39" s="56"/>
-      <c r="Q39" s="57"/>
-      <c r="R39" s="58"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="29"/>
+      <c r="N39" s="56"/>
+      <c r="O39" s="57"/>
+      <c r="P39" s="58"/>
+      <c r="Q39" s="27"/>
+      <c r="R39" s="29"/>
       <c r="S39" s="34"/>
     </row>
   </sheetData>
@@ -5235,9 +5307,9 @@
     <mergeCell ref="D4:J4"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="S4:S5"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="K4:M4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/report/MonthReport.xlsx
+++ b/public/report/MonthReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\test\SEEMS_EMS\public\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hdrenewables-my.sharepoint.com/personal/hugo_huang_hdrenewables_com/Documents/2.案場資料/1.專案開發/3.表前-花蓮三案/E-dReg-10M+10M/8.報表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF5A07C-7D24-41E9-973C-48C76CB6B2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{7FF5A07C-7D24-41E9-973C-48C76CB6B2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2730B7D1-77A8-4972-8353-DE00F55AADF2}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="735" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-190" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="圖表" sheetId="3" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>日
 (Day)</t>
@@ -99,10 +99,6 @@
   </si>
   <si>
     <t>Net</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>總用電量 (MWh)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -152,9 +148,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ESS1-2</t>
-  </si>
-  <si>
     <t>ESS2-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -191,16 +184,31 @@
     <t>月報</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>ESS1-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUX-MVCB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去年同期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>總用電量 (KWh)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0.0_ "/>
-    <numFmt numFmtId="177" formatCode="0.0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,27 +226,60 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="136"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="50">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -292,21 +333,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -490,21 +516,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -573,6 +584,99 @@
       </left>
       <right/>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -582,12 +686,10 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -598,199 +700,8 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -834,46 +745,76 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="medium">
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -883,7 +824,48 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -892,263 +874,271 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2042,7 +2032,7 @@
             <c:numRef>
               <c:f>數值!$M$6:$M$36</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="31"/>
               </c:numCache>
             </c:numRef>
@@ -2197,7 +2187,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4323,97 +4313,105 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="C2:L8"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="C2:M8"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="8.75" style="1"/>
-    <col min="3" max="3" width="17.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.75" style="1"/>
+    <col min="1" max="2" width="8.7109375" style="1"/>
+    <col min="3" max="3" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" style="1" customWidth="1"/>
+    <col min="5" max="12" width="14" style="1" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:12" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="62"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61" t="s">
+    <row r="2" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="35"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61" t="s">
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="37"/>
+    </row>
+    <row r="4" spans="3:13" s="2" customFormat="1" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="71" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="73" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="61" t="s">
+      <c r="G4" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="79" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="79" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="61"/>
-      <c r="L3" s="63"/>
     </row>
-    <row r="4" spans="3:12" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="66" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="74" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="70" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="74" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="70" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="74" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="70" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="72" t="s">
-        <v>26</v>
-      </c>
+    <row r="5" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="72"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="69"/>
     </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C5" s="67"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="73"/>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C6" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="34"/>
     </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C6" s="60" t="s">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C7" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="5"/>
-    </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="7"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -4421,35 +4419,38 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="5"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="64"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="9"/>
+    <row r="8" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="M4:M5"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="L4:L5"/>
-    <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
+    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4464,842 +4465,843 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="C2:S39"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="8.75" style="1"/>
-    <col min="3" max="3" width="8.75" style="2" customWidth="1"/>
-    <col min="4" max="10" width="7.625" style="2" customWidth="1"/>
-    <col min="11" max="12" width="10.125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.7109375" style="1"/>
+    <col min="3" max="3" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="7.5703125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10.140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.75" style="1"/>
+    <col min="19" max="19" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="3:19" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="62"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61" t="s">
+    <row r="3" spans="3:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="26"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="61" t="s">
+      <c r="O3" s="60"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="61"/>
+    </row>
+    <row r="4" spans="3:19" s="2" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="89" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="91"/>
+      <c r="M4" s="90"/>
+      <c r="N4" s="89" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" s="91"/>
+      <c r="P4" s="90"/>
+      <c r="Q4" s="89" t="s">
+        <v>11</v>
+      </c>
+      <c r="R4" s="90"/>
+      <c r="S4" s="87" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="86"/>
+      <c r="D5" s="62">
+        <v>1</v>
+      </c>
+      <c r="E5" s="63">
+        <v>0.8</v>
+      </c>
+      <c r="F5" s="63">
+        <v>0.6</v>
+      </c>
+      <c r="G5" s="63">
+        <v>0.4</v>
+      </c>
+      <c r="H5" s="63">
+        <v>0.2</v>
+      </c>
+      <c r="I5" s="63">
+        <v>0</v>
+      </c>
+      <c r="J5" s="64">
+        <v>-1</v>
+      </c>
+      <c r="K5" s="65" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="M5" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="O5" s="66" t="s">
+        <v>7</v>
+      </c>
+      <c r="P5" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q5" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="R5" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="S5" s="88"/>
+    </row>
+    <row r="6" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C6" s="27">
+        <v>1</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="21"/>
+      <c r="S6" s="22"/>
+    </row>
+    <row r="7" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C7" s="28">
+        <v>2</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="22"/>
+    </row>
+    <row r="8" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C8" s="28">
+        <v>3</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="22"/>
+    </row>
+    <row r="9" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C9" s="28">
+        <v>4</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="22"/>
+    </row>
+    <row r="10" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C10" s="28">
+        <v>5</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="22"/>
+    </row>
+    <row r="11" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C11" s="28">
+        <v>6</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="22"/>
+    </row>
+    <row r="12" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C12" s="28">
+        <v>7</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="22"/>
+    </row>
+    <row r="13" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C13" s="28">
+        <v>8</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="22"/>
+    </row>
+    <row r="14" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C14" s="28">
+        <v>9</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="22"/>
+    </row>
+    <row r="15" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C15" s="28">
+        <v>10</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="22"/>
+    </row>
+    <row r="16" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C16" s="28">
+        <v>11</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="22"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C17" s="28">
+        <v>12</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="22"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C18" s="28">
+        <v>13</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="22"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C19" s="28">
+        <v>14</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="21"/>
+      <c r="S19" s="22"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C20" s="28">
+        <v>15</v>
+      </c>
+      <c r="D20" s="11"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="21"/>
+      <c r="S20" s="22"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C21" s="28">
+        <v>16</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="21"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="21"/>
+      <c r="S21" s="22"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C22" s="28">
+        <v>17</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="21"/>
+      <c r="S22" s="22"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C23" s="28">
+        <v>18</v>
+      </c>
+      <c r="D23" s="11"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="21"/>
+      <c r="S23" s="22"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C24" s="28">
+        <v>19</v>
+      </c>
+      <c r="D24" s="11"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="22"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C25" s="28">
+        <v>20</v>
+      </c>
+      <c r="D25" s="11"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="21"/>
+      <c r="S25" s="22"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C26" s="28">
+        <v>21</v>
+      </c>
+      <c r="D26" s="11"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="21"/>
+      <c r="S26" s="22"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C27" s="28">
+        <v>22</v>
+      </c>
+      <c r="D27" s="11"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="21"/>
+      <c r="S27" s="22"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C28" s="28">
+        <v>23</v>
+      </c>
+      <c r="D28" s="11"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="21"/>
+      <c r="S28" s="22"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C29" s="28">
+        <v>24</v>
+      </c>
+      <c r="D29" s="11"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="21"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="21"/>
+      <c r="S29" s="22"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C30" s="28">
+        <v>25</v>
+      </c>
+      <c r="D30" s="11"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="21"/>
+      <c r="S30" s="22"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C31" s="28">
+        <v>26</v>
+      </c>
+      <c r="D31" s="11"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="21"/>
+      <c r="S31" s="22"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C32" s="28">
+        <v>27</v>
+      </c>
+      <c r="D32" s="11"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="21"/>
+      <c r="S32" s="22"/>
+    </row>
+    <row r="33" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C33" s="28">
+        <v>28</v>
+      </c>
+      <c r="D33" s="11"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="21"/>
+      <c r="S33" s="22"/>
+    </row>
+    <row r="34" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C34" s="28">
         <v>29</v>
       </c>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="61" t="s">
+      <c r="D34" s="11"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="21"/>
+      <c r="S34" s="22"/>
+    </row>
+    <row r="35" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C35" s="28">
         <v>30</v>
       </c>
-      <c r="O3" s="61"/>
-      <c r="P3" s="61"/>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="61"/>
-      <c r="S3" s="63"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="20"/>
+      <c r="R35" s="21"/>
+      <c r="S35" s="22"/>
     </row>
-    <row r="4" spans="3:19" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="83" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" s="84"/>
-      <c r="M4" s="85"/>
-      <c r="N4" s="83" t="s">
+    <row r="36" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="29">
+        <v>31</v>
+      </c>
+      <c r="D36" s="14"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="23"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="24"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="24"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="24"/>
+      <c r="S36" s="25"/>
+    </row>
+    <row r="37" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="O4" s="84"/>
-      <c r="P4" s="85"/>
-      <c r="Q4" s="78" t="s">
-        <v>12</v>
-      </c>
-      <c r="R4" s="82"/>
-      <c r="S4" s="80" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="79"/>
-      <c r="D5" s="7">
-        <v>1</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.8</v>
-      </c>
-      <c r="F5" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="G5" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="H5" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="I5" s="8">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9">
-        <v>-1</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="L5" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="M5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="O5" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="P5" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q5" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="R5" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="S5" s="81"/>
-    </row>
-    <row r="6" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C6" s="17">
-        <v>1</v>
-      </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="44"/>
-    </row>
-    <row r="7" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C7" s="16">
-        <v>2</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="45"/>
-    </row>
-    <row r="8" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C8" s="16">
-        <v>3</v>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="39"/>
-      <c r="S8" s="45"/>
-    </row>
-    <row r="9" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C9" s="16">
-        <v>4</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="42"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="39"/>
-      <c r="S9" s="45"/>
-    </row>
-    <row r="10" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C10" s="16">
-        <v>5</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="39"/>
-      <c r="S10" s="45"/>
-    </row>
-    <row r="11" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C11" s="16">
-        <v>6</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="42"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="45"/>
-    </row>
-    <row r="12" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C12" s="16">
-        <v>7</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="45"/>
-    </row>
-    <row r="13" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C13" s="16">
-        <v>8</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="39"/>
-      <c r="S13" s="45"/>
-    </row>
-    <row r="14" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C14" s="16">
-        <v>9</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="39"/>
-      <c r="S14" s="45"/>
-    </row>
-    <row r="15" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C15" s="16">
-        <v>10</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="39"/>
-      <c r="S15" s="45"/>
-    </row>
-    <row r="16" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C16" s="16">
-        <v>11</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="39"/>
-      <c r="S16" s="45"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C17" s="16">
-        <v>12</v>
-      </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="39"/>
-      <c r="S17" s="45"/>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C18" s="16">
-        <v>13</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="39"/>
-      <c r="S18" s="45"/>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C19" s="16">
-        <v>14</v>
-      </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="39"/>
-      <c r="S19" s="45"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C20" s="16">
-        <v>15</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="39"/>
-      <c r="S20" s="45"/>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C21" s="16">
-        <v>16</v>
-      </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="39"/>
-      <c r="S21" s="45"/>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C22" s="16">
-        <v>17</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="39"/>
-      <c r="S22" s="45"/>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C23" s="16">
-        <v>18</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="36"/>
-      <c r="R23" s="39"/>
-      <c r="S23" s="45"/>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C24" s="16">
-        <v>19</v>
-      </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="36"/>
-      <c r="R24" s="39"/>
-      <c r="S24" s="45"/>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C25" s="16">
-        <v>20</v>
-      </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="36"/>
-      <c r="R25" s="39"/>
-      <c r="S25" s="45"/>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C26" s="16">
-        <v>21</v>
-      </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="36"/>
-      <c r="R26" s="39"/>
-      <c r="S26" s="45"/>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C27" s="16">
-        <v>22</v>
-      </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="36"/>
-      <c r="R27" s="39"/>
-      <c r="S27" s="45"/>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C28" s="16">
-        <v>23</v>
-      </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="36"/>
-      <c r="R28" s="39"/>
-      <c r="S28" s="45"/>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C29" s="16">
-        <v>24</v>
-      </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="36"/>
-      <c r="R29" s="39"/>
-      <c r="S29" s="45"/>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C30" s="16">
-        <v>25</v>
-      </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="36"/>
-      <c r="R30" s="39"/>
-      <c r="S30" s="45"/>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C31" s="16">
-        <v>26</v>
-      </c>
-      <c r="D31" s="6"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="36"/>
-      <c r="R31" s="39"/>
-      <c r="S31" s="45"/>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C32" s="16">
-        <v>27</v>
-      </c>
-      <c r="D32" s="6"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="36"/>
-      <c r="R32" s="39"/>
-      <c r="S32" s="45"/>
-    </row>
-    <row r="33" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C33" s="16">
-        <v>28</v>
-      </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="42"/>
-      <c r="Q33" s="36"/>
-      <c r="R33" s="39"/>
-      <c r="S33" s="45"/>
-    </row>
-    <row r="34" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C34" s="16">
-        <v>29</v>
-      </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="15"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="42"/>
-      <c r="Q34" s="36"/>
-      <c r="R34" s="39"/>
-      <c r="S34" s="45"/>
-    </row>
-    <row r="35" spans="3:19" x14ac:dyDescent="0.3">
-      <c r="C35" s="16">
-        <v>30</v>
-      </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="42"/>
-      <c r="Q35" s="36"/>
-      <c r="R35" s="39"/>
-      <c r="S35" s="45"/>
-    </row>
-    <row r="36" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="30">
-        <v>31</v>
-      </c>
-      <c r="D36" s="10"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="31"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="31"/>
-      <c r="O36" s="33"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="37"/>
-      <c r="R36" s="40"/>
-      <c r="S36" s="46"/>
-    </row>
-    <row r="37" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="49"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="50"/>
-      <c r="I37" s="50"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
       <c r="J37" s="51"/>
       <c r="K37" s="54"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="51"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="52"/>
-      <c r="R37" s="59"/>
-      <c r="S37" s="55"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="44"/>
+      <c r="N37" s="54"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="44"/>
+      <c r="Q37" s="54"/>
+      <c r="R37" s="44"/>
+      <c r="S37" s="57"/>
     </row>
-    <row r="38" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C38" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38" s="27"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="29"/>
-      <c r="N38" s="56"/>
-      <c r="O38" s="57"/>
-      <c r="P38" s="58"/>
-      <c r="Q38" s="27"/>
-      <c r="R38" s="29"/>
-      <c r="S38" s="34"/>
+    <row r="38" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="45"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="55"/>
+      <c r="L38" s="40"/>
+      <c r="M38" s="46"/>
+      <c r="N38" s="55"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="46"/>
+      <c r="Q38" s="55"/>
+      <c r="R38" s="46"/>
+      <c r="S38" s="58"/>
     </row>
-    <row r="39" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C39" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="27"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="29"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="29"/>
+    <row r="39" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="47"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="56"/>
+      <c r="L39" s="49"/>
+      <c r="M39" s="50"/>
       <c r="N39" s="56"/>
-      <c r="O39" s="57"/>
-      <c r="P39" s="58"/>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="29"/>
-      <c r="S39" s="34"/>
+      <c r="O39" s="49"/>
+      <c r="P39" s="50"/>
+      <c r="Q39" s="56"/>
+      <c r="R39" s="50"/>
+      <c r="S39" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/public/report/MonthReport.xlsx
+++ b/public/report/MonthReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hdrenewables-my.sharepoint.com/personal/hugo_huang_hdrenewables_com/Documents/2.案場資料/1.專案開發/3.表前-花蓮三案/E-dReg-10M+10M/8.報表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{7FF5A07C-7D24-41E9-973C-48C76CB6B2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2730B7D1-77A8-4972-8353-DE00F55AADF2}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="13_ncr:1_{7FF5A07C-7D24-41E9-973C-48C76CB6B2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F3FECDF-F3BE-428F-AB6C-A7AE9E99AA8C}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-190" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="圖表" sheetId="3" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>日
 (Day)</t>
@@ -198,6 +198,10 @@
   </si>
   <si>
     <t>總用電量 (KWh)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>花蓮和平10MW 地號4-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4490,7 +4494,7 @@
       <c r="E3" s="60"/>
       <c r="F3" s="60"/>
       <c r="G3" s="60" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H3" s="60"/>
       <c r="I3" s="60"/>

--- a/public/report/MonthReport.xlsx
+++ b/public/report/MonthReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hdrenewables-my.sharepoint.com/personal/hugo_huang_hdrenewables_com/Documents/2.案場資料/1.專案開發/3.表前-花蓮三案/E-dReg-10M+10M/8.報表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="13_ncr:1_{7FF5A07C-7D24-41E9-973C-48C76CB6B2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F3FECDF-F3BE-428F-AB6C-A7AE9E99AA8C}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{7FF5A07C-7D24-41E9-973C-48C76CB6B2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A292DE8-4FD1-469B-AA73-9DC7508CA368}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -168,15 +168,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>輔助用電分析
-(kWh)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>花蓮和平10MW</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>E-dReg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -197,11 +188,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>總用電量 (KWh)</t>
+    <t>花蓮和平10MW 地號13-21</t>
+  </si>
+  <si>
+    <t>花蓮和平10MW 地號4-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>花蓮和平10MW 地號4-1</t>
+    <t>總用電量 (MWh)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輔助用電分析
+(單位: kWh)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -881,7 +880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -902,7 +901,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4330,89 +4328,89 @@
   <sheetData>
     <row r="2" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="3:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36" t="s">
+      <c r="C3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="37"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="36"/>
     </row>
     <row r="4" spans="3:13" s="2" customFormat="1" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="71" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="73" t="s">
+      <c r="C4" s="70" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="79" t="s">
+      <c r="E4" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="79" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="75" t="s">
+      <c r="F4" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="79" t="s">
+      <c r="H4" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="75" t="s">
+      <c r="I4" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="79" t="s">
+      <c r="J4" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="75" t="s">
+      <c r="K4" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="77" t="s">
+      <c r="L4" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="M4" s="68" t="s">
-        <v>30</v>
+      <c r="M4" s="67" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="72"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="69"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="68"/>
     </row>
     <row r="6" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="34"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="33"/>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="30" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="7"/>
@@ -4427,10 +4425,10 @@
       <c r="M7" s="4"/>
     </row>
     <row r="8" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="8"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -4489,823 +4487,823 @@
       <c r="S2" s="1"/>
     </row>
     <row r="3" spans="3:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="26"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="61"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="59" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="60"/>
     </row>
     <row r="4" spans="3:19" s="2" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="85" t="s">
+      <c r="C4" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="82" t="s">
+      <c r="D4" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="89" t="s">
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="91"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="89" t="s">
+      <c r="L4" s="90"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="O4" s="91"/>
-      <c r="P4" s="90"/>
-      <c r="Q4" s="89" t="s">
+      <c r="O4" s="90"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="R4" s="90"/>
-      <c r="S4" s="87" t="s">
+      <c r="R4" s="89"/>
+      <c r="S4" s="86" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="86"/>
-      <c r="D5" s="62">
+      <c r="C5" s="85"/>
+      <c r="D5" s="61">
         <v>1</v>
       </c>
-      <c r="E5" s="63">
+      <c r="E5" s="62">
         <v>0.8</v>
       </c>
-      <c r="F5" s="63">
+      <c r="F5" s="62">
         <v>0.6</v>
       </c>
-      <c r="G5" s="63">
+      <c r="G5" s="62">
         <v>0.4</v>
       </c>
-      <c r="H5" s="63">
+      <c r="H5" s="62">
         <v>0.2</v>
       </c>
-      <c r="I5" s="63">
+      <c r="I5" s="62">
         <v>0</v>
       </c>
-      <c r="J5" s="64">
+      <c r="J5" s="63">
         <v>-1</v>
       </c>
-      <c r="K5" s="65" t="s">
+      <c r="K5" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="66" t="s">
+      <c r="L5" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="M5" s="67" t="s">
+      <c r="M5" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="N5" s="65" t="s">
+      <c r="N5" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="66" t="s">
+      <c r="O5" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="P5" s="67" t="s">
+      <c r="P5" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="65" t="s">
+      <c r="Q5" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="R5" s="67" t="s">
+      <c r="R5" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="S5" s="88"/>
+      <c r="S5" s="87"/>
     </row>
     <row r="6" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <v>1</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="21"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="21"/>
-      <c r="S6" s="22"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="21"/>
     </row>
     <row r="7" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C7" s="28">
+      <c r="C7" s="27">
         <v>2</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="22"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="21"/>
     </row>
     <row r="8" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C8" s="28">
+      <c r="C8" s="27">
         <v>3</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="22"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="21"/>
     </row>
     <row r="9" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C9" s="28">
+      <c r="C9" s="27">
         <v>4</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="22"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="21"/>
     </row>
     <row r="10" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C10" s="28">
+      <c r="C10" s="27">
         <v>5</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="21"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="21"/>
-      <c r="S10" s="22"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="21"/>
     </row>
     <row r="11" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C11" s="28">
+      <c r="C11" s="27">
         <v>6</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="22"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="21"/>
     </row>
     <row r="12" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C12" s="28">
+      <c r="C12" s="27">
         <v>7</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="22"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="21"/>
     </row>
     <row r="13" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C13" s="28">
+      <c r="C13" s="27">
         <v>8</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="22"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="21"/>
     </row>
     <row r="14" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C14" s="28">
+      <c r="C14" s="27">
         <v>9</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="22"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="21"/>
     </row>
     <row r="15" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C15" s="28">
+      <c r="C15" s="27">
         <v>10</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="22"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="21"/>
     </row>
     <row r="16" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C16" s="28">
+      <c r="C16" s="27">
         <v>11</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="21"/>
-      <c r="S16" s="22"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="21"/>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C17" s="28">
+      <c r="C17" s="27">
         <v>12</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="22"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="21"/>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C18" s="28">
+      <c r="C18" s="27">
         <v>13</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="22"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="21"/>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C19" s="28">
+      <c r="C19" s="27">
         <v>14</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="21"/>
-      <c r="S19" s="22"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="21"/>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C20" s="28">
+      <c r="C20" s="27">
         <v>15</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="21"/>
-      <c r="S20" s="22"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="21"/>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C21" s="28">
+      <c r="C21" s="27">
         <v>16</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="21"/>
-      <c r="S21" s="22"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="21"/>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C22" s="28">
+      <c r="C22" s="27">
         <v>17</v>
       </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="22"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="21"/>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C23" s="28">
+      <c r="C23" s="27">
         <v>18</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="21"/>
-      <c r="S23" s="22"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="21"/>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C24" s="28">
+      <c r="C24" s="27">
         <v>19</v>
       </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="22"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="21"/>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C25" s="28">
+      <c r="C25" s="27">
         <v>20</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="22"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="12"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="21"/>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C26" s="28">
+      <c r="C26" s="27">
         <v>21</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="22"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="21"/>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C27" s="28">
+      <c r="C27" s="27">
         <v>22</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="18"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="21"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="21"/>
-      <c r="S27" s="22"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="12"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="21"/>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C28" s="28">
+      <c r="C28" s="27">
         <v>23</v>
       </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="21"/>
-      <c r="S28" s="22"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="21"/>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C29" s="28">
+      <c r="C29" s="27">
         <v>24</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="21"/>
-      <c r="S29" s="22"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="21"/>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C30" s="28">
+      <c r="C30" s="27">
         <v>25</v>
       </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="20"/>
-      <c r="O30" s="13"/>
-      <c r="P30" s="21"/>
-      <c r="Q30" s="20"/>
-      <c r="R30" s="21"/>
-      <c r="S30" s="22"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="21"/>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C31" s="28">
+      <c r="C31" s="27">
         <v>26</v>
       </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="21"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="21"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="21"/>
-      <c r="S31" s="22"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="21"/>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C32" s="28">
+      <c r="C32" s="27">
         <v>27</v>
       </c>
-      <c r="D32" s="11"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="21"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="13"/>
-      <c r="P32" s="21"/>
-      <c r="Q32" s="20"/>
-      <c r="R32" s="21"/>
-      <c r="S32" s="22"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="21"/>
     </row>
     <row r="33" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C33" s="28">
+      <c r="C33" s="27">
         <v>28</v>
       </c>
-      <c r="D33" s="11"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="13"/>
-      <c r="P33" s="21"/>
-      <c r="Q33" s="20"/>
-      <c r="R33" s="21"/>
-      <c r="S33" s="22"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="12"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="21"/>
     </row>
     <row r="34" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C34" s="28">
+      <c r="C34" s="27">
         <v>29</v>
       </c>
-      <c r="D34" s="11"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="21"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="21"/>
-      <c r="Q34" s="20"/>
-      <c r="R34" s="21"/>
-      <c r="S34" s="22"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="12"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="21"/>
     </row>
     <row r="35" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C35" s="28">
+      <c r="C35" s="27">
         <v>30</v>
       </c>
-      <c r="D35" s="11"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="21"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="21"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="21"/>
-      <c r="S35" s="22"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="12"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="19"/>
+      <c r="R35" s="20"/>
+      <c r="S35" s="21"/>
     </row>
     <row r="36" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="29">
+      <c r="C36" s="28">
         <v>31</v>
       </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="24"/>
-      <c r="N36" s="23"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="24"/>
-      <c r="Q36" s="23"/>
-      <c r="R36" s="24"/>
-      <c r="S36" s="25"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="23"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="23"/>
+      <c r="Q36" s="22"/>
+      <c r="R36" s="23"/>
+      <c r="S36" s="24"/>
     </row>
     <row r="37" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="38" t="s">
+      <c r="C37" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="41"/>
-      <c r="E37" s="42"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="42"/>
-      <c r="I37" s="42"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="54"/>
-      <c r="L37" s="43"/>
-      <c r="M37" s="44"/>
-      <c r="N37" s="54"/>
-      <c r="O37" s="43"/>
-      <c r="P37" s="44"/>
-      <c r="Q37" s="54"/>
-      <c r="R37" s="44"/>
-      <c r="S37" s="57"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="42"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="53"/>
+      <c r="O37" s="42"/>
+      <c r="P37" s="43"/>
+      <c r="Q37" s="53"/>
+      <c r="R37" s="43"/>
+      <c r="S37" s="56"/>
     </row>
     <row r="38" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="38" t="s">
+      <c r="C38" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="D38" s="45"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="55"/>
-      <c r="L38" s="40"/>
-      <c r="M38" s="46"/>
-      <c r="N38" s="55"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="46"/>
-      <c r="Q38" s="55"/>
-      <c r="R38" s="46"/>
-      <c r="S38" s="58"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="51"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="45"/>
+      <c r="N38" s="54"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="45"/>
+      <c r="Q38" s="54"/>
+      <c r="R38" s="45"/>
+      <c r="S38" s="57"/>
     </row>
     <row r="39" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="D39" s="47"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48"/>
-      <c r="J39" s="53"/>
-      <c r="K39" s="56"/>
-      <c r="L39" s="49"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="56"/>
-      <c r="O39" s="49"/>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="56"/>
-      <c r="R39" s="50"/>
-      <c r="S39" s="59"/>
+      <c r="C39" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="46"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="47"/>
+      <c r="I39" s="47"/>
+      <c r="J39" s="52"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="48"/>
+      <c r="M39" s="49"/>
+      <c r="N39" s="55"/>
+      <c r="O39" s="48"/>
+      <c r="P39" s="49"/>
+      <c r="Q39" s="55"/>
+      <c r="R39" s="49"/>
+      <c r="S39" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="7">
